--- a/data/similarity_score.xlsx
+++ b/data/similarity_score.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ayush_Kumar_Resume(LLumo)_text.txt</t>
+          <t>ayushResume_text.txt</t>
         </is>
       </c>
     </row>
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.9999999999999911</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3423101593909587</v>
+        <v>0.3137540601024053</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1355159571112085</v>
+        <v>0.08222127496601987</v>
       </c>
     </row>
     <row r="3">
@@ -468,26 +468,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3423101593909587</v>
+        <v>0.3137540601024053</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2653347785473592</v>
+        <v>0.2791477288028112</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Ayush_Kumar_Resume(LLumo)_text.txt</t>
+          <t>ayushResume_text.txt</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1355159571112085</v>
+        <v>0.08222127496601987</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2653347785473592</v>
+        <v>0.2791477288028112</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>

--- a/data/similarity_score.xlsx
+++ b/data/similarity_score.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999999999999911</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3137540601024053</v>
+        <v>0.3760249467109673</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08222127496601987</v>
+        <v>0.0993356588769921</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3137540601024053</v>
+        <v>0.3760249467109673</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2791477288028112</v>
+        <v>0.2751568928230297</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08222127496601987</v>
+        <v>0.0993356588769921</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2791477288028112</v>
+        <v>0.2751568928230297</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>

--- a/data/similarity_score.xlsx
+++ b/data/similarity_score.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>ayushResume_text.txt</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>IMG_20240724_221056_text.txt</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -452,13 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3760249467109673</v>
+        <v>0.2283639567073452</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0993356588769921</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1592514469996917</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +476,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3760249467109673</v>
+        <v>0.2283639567073452</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9999999999999996</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2751568928230297</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4615798428045873</v>
       </c>
     </row>
     <row r="4">
@@ -484,12 +495,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0993356588769921</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2751568928230297</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>IMG_20240724_221056_text.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1592514469996917</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4615798428045873</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>
